--- a/rules/CORE-000531/negative/01/data/unit-test-coreid-CG0126-negative.xlsx
+++ b/rules/CORE-000531/negative/01/data/unit-test-coreid-CG0126-negative.xlsx
@@ -37,7 +37,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -58,7 +58,7 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
+      <i/>
     </font>
     <font>
       <sz val="11"/>
@@ -77,8 +77,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -91,6 +95,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFFFCC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -102,12 +107,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -137,7 +149,7 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -148,6 +160,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -490,7 +503,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="4" t="str">
         <v>sdtmig</v>
       </c>
       <c r="B2" s="4" t="str">
@@ -517,18 +530,18 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="4" t="str">
         <v>dm.xpt</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="4" t="str">
         <v>Demographics</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="str">
+      <c r="A3" s="4" t="str">
         <v>ta.xpt</v>
       </c>
-      <c r="B3" s="2" t="str">
+      <c r="B3" s="4" t="str">
         <v>Trial Arms</v>
       </c>
     </row>
@@ -564,42 +577,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="4" t="str">
         <v>dm.xpt</v>
       </c>
-      <c r="C2" s="2" t="str">
+      <c r="C2" s="4" t="str">
         <v>Record</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="4">
         <v>14</v>
       </c>
-      <c r="E2" s="2" t="str">
+      <c r="E2" s="4" t="str">
         <v>ARMCD</v>
       </c>
-      <c r="F2" s="2" t="str">
+      <c r="F2" s="4" t="str">
         <v>ZAN_MED</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="str">
+      <c r="B3" s="4" t="str">
         <v>dm.xpt</v>
       </c>
-      <c r="C3" s="2" t="str">
+      <c r="C3" s="4" t="str">
         <v>Record</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="4">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="str">
+      <c r="E3" s="4" t="str">
         <v>ARMCD</v>
       </c>
-      <c r="F3" s="2" t="str">
+      <c r="F3" s="4" t="str">
         <v>ZAN_UNK</v>
       </c>
     </row>
@@ -618,9 +631,6 @@
       </c>
       <c r="E4" s="2" t="str">
         <v>ARMCD</v>
-      </c>
-      <c r="F4" s="2" t="str">
-        <v>[ABSENT]</v>
       </c>
     </row>
   </sheetData>
@@ -665,10 +675,10 @@
       <c r="J1" s="3" t="str">
         <v>RFPENDTC</v>
       </c>
-      <c r="K1" s="5" t="str">
+      <c r="K1" s="3" t="str">
         <v>DTHDTC</v>
       </c>
-      <c r="L1" s="5" t="str">
+      <c r="L1" s="3" t="str">
         <v>DTHFL</v>
       </c>
       <c r="M1" s="3" t="str">
@@ -695,16 +705,16 @@
       <c r="T1" s="3" t="str">
         <v>ETHNIC</v>
       </c>
-      <c r="U1" s="5" t="str">
+      <c r="U1" s="3" t="str">
         <v>ARMCD</v>
       </c>
       <c r="V1" s="3" t="str">
         <v>ARM</v>
       </c>
-      <c r="W1" s="5" t="str">
+      <c r="W1" s="3" t="str">
         <v>ACTARMCD</v>
       </c>
-      <c r="X1" s="5" t="str">
+      <c r="X1" s="3" t="str">
         <v>ACTARM</v>
       </c>
       <c r="Y1" s="3" t="str">
@@ -712,7 +722,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="str">
+      <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
       <c r="B2" s="6" t="str">
@@ -943,10 +953,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="str">
+      <c r="A5" s="4" t="str">
         <v>ABC</v>
       </c>
-      <c r="B5" s="2" t="str">
+      <c r="B5" s="4" t="str">
         <v>DM</v>
       </c>
       <c r="C5" s="4" t="str">
@@ -973,10 +983,10 @@
       <c r="J5" s="4" t="str">
         <v>2021-02-18</v>
       </c>
-      <c r="K5" s="7" t="str">
+      <c r="K5" s="4" t="str">
         <v>2021-02-18</v>
       </c>
-      <c r="L5" s="7" t="str">
+      <c r="L5" s="4" t="str">
         <v/>
       </c>
       <c r="M5" s="4" t="str">
@@ -985,13 +995,13 @@
       <c r="N5" s="4" t="str">
         <v>1940-01-14</v>
       </c>
-      <c r="O5" s="7">
+      <c r="O5" s="4">
         <v>78</v>
       </c>
-      <c r="P5" s="7" t="str">
-        <v/>
-      </c>
-      <c r="Q5" s="7" t="str">
+      <c r="P5" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Q5" s="4" t="str">
         <v>YEARS</v>
       </c>
       <c r="R5" s="4" t="str">
@@ -1003,16 +1013,16 @@
       <c r="T5" s="4" t="str">
         <v>HISPANIC OR LATINO</v>
       </c>
-      <c r="U5" s="7" t="str">
+      <c r="U5" s="4" t="str">
         <v>SCRNFAIL</v>
       </c>
-      <c r="V5" s="7" t="str">
+      <c r="V5" s="4" t="str">
         <v>Screen Failure</v>
       </c>
-      <c r="W5" s="7" t="str">
+      <c r="W5" s="4" t="str">
         <v>SCRNFAIL</v>
       </c>
-      <c r="X5" s="7" t="str">
+      <c r="X5" s="4" t="str">
         <v>Screen Failure</v>
       </c>
       <c r="Y5" s="4" t="str">
@@ -1020,10 +1030,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="str">
+      <c r="A6" s="4" t="str">
         <v>ABC</v>
       </c>
-      <c r="B6" s="2" t="str">
+      <c r="B6" s="4" t="str">
         <v>DM</v>
       </c>
       <c r="C6" s="4" t="str">
@@ -1050,10 +1060,10 @@
       <c r="J6" s="4" t="str">
         <v>2018-09-04</v>
       </c>
-      <c r="K6" s="7" t="str">
+      <c r="K6" s="4" t="str">
         <v>2018-09-04</v>
       </c>
-      <c r="L6" s="7" t="str">
+      <c r="L6" s="4" t="str">
         <v>N</v>
       </c>
       <c r="M6" s="4" t="str">
@@ -1062,13 +1072,13 @@
       <c r="N6" s="4" t="str">
         <v>1947-12-23</v>
       </c>
-      <c r="O6" s="7">
+      <c r="O6" s="4">
         <v>70</v>
       </c>
-      <c r="P6" s="7" t="str">
-        <v/>
-      </c>
-      <c r="Q6" s="7" t="str">
+      <c r="P6" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Q6" s="4" t="str">
         <v>YEARS</v>
       </c>
       <c r="R6" s="4" t="str">
@@ -1080,16 +1090,16 @@
       <c r="T6" s="4" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="U6" s="7" t="str">
+      <c r="U6" s="4" t="str">
         <v>NOTASSGN</v>
       </c>
-      <c r="V6" s="7" t="str">
+      <c r="V6" s="4" t="str">
         <v>Not Assigned</v>
       </c>
-      <c r="W6" s="7" t="str">
+      <c r="W6" s="4" t="str">
         <v>NOTASSGN</v>
       </c>
-      <c r="X6" s="7" t="str">
+      <c r="X6" s="4" t="str">
         <v>Not Assigned</v>
       </c>
       <c r="Y6" s="4" t="str">
@@ -1097,10 +1107,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="str">
+      <c r="A7" s="4" t="str">
         <v>ABC</v>
       </c>
-      <c r="B7" s="2" t="str">
+      <c r="B7" s="4" t="str">
         <v>DM</v>
       </c>
       <c r="C7" s="4" t="str">
@@ -1127,7 +1137,7 @@
       <c r="J7" s="4" t="str">
         <v>2018-09-04</v>
       </c>
-      <c r="K7" s="7" t="str">
+      <c r="K7" s="4" t="str">
         <v>2019-11-18</v>
       </c>
       <c r="L7" s="4" t="str">
@@ -1139,13 +1149,13 @@
       <c r="N7" s="4" t="str">
         <v>1947-12-23</v>
       </c>
-      <c r="O7" s="7">
+      <c r="O7" s="4">
         <v>71</v>
       </c>
-      <c r="P7" s="7" t="str">
-        <v/>
-      </c>
-      <c r="Q7" s="7" t="str">
+      <c r="P7" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Q7" s="4" t="str">
         <v>YEARS</v>
       </c>
       <c r="R7" s="4" t="str">
@@ -1157,16 +1167,16 @@
       <c r="T7" s="4" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="U7" s="7" t="str">
+      <c r="U7" s="4" t="str">
         <v>PLACEBO</v>
       </c>
-      <c r="V7" s="7" t="str">
+      <c r="V7" s="4" t="str">
         <v>Placebo</v>
       </c>
-      <c r="W7" s="7" t="str">
+      <c r="W7" s="4" t="str">
         <v>PLACEBO</v>
       </c>
-      <c r="X7" s="7" t="str">
+      <c r="X7" s="4" t="str">
         <v>Placebo</v>
       </c>
       <c r="Y7" s="4" t="str">
@@ -1174,10 +1184,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="str">
+      <c r="A8" s="4" t="str">
         <v>ABC</v>
       </c>
-      <c r="B8" s="2" t="str">
+      <c r="B8" s="4" t="str">
         <v>DM</v>
       </c>
       <c r="C8" s="4" t="str">
@@ -1204,10 +1214,10 @@
       <c r="J8" s="4" t="str">
         <v>2021-02-18</v>
       </c>
-      <c r="K8" s="7" t="str">
+      <c r="K8" s="4" t="str">
         <v>2021-02-18</v>
       </c>
-      <c r="L8" s="7" t="str">
+      <c r="L8" s="4" t="str">
         <v/>
       </c>
       <c r="M8" s="4" t="str">
@@ -1216,13 +1226,13 @@
       <c r="N8" s="4" t="str">
         <v>1940-01-14</v>
       </c>
-      <c r="O8" s="7">
+      <c r="O8" s="4">
         <v>78</v>
       </c>
-      <c r="P8" s="7" t="str">
-        <v/>
-      </c>
-      <c r="Q8" s="7" t="str">
+      <c r="P8" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Q8" s="4" t="str">
         <v>YEARS</v>
       </c>
       <c r="R8" s="4" t="str">
@@ -1240,10 +1250,10 @@
       <c r="V8" s="4" t="str">
         <v>Zanomaline Low Dose (54 mg)</v>
       </c>
-      <c r="W8" s="7" t="str">
+      <c r="W8" s="4" t="str">
         <v>NOTTRT</v>
       </c>
-      <c r="X8" s="7" t="str">
+      <c r="X8" s="4" t="str">
         <v>Not Treated</v>
       </c>
       <c r="Y8" s="4" t="str">
@@ -1251,10 +1261,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="str">
+      <c r="A9" s="4" t="str">
         <v>ABC</v>
       </c>
-      <c r="B9" s="2" t="str">
+      <c r="B9" s="4" t="str">
         <v>DM</v>
       </c>
       <c r="C9" s="4" t="str">
@@ -1281,10 +1291,10 @@
       <c r="J9" s="4" t="str">
         <v>2021-02-18</v>
       </c>
-      <c r="K9" s="7" t="str">
+      <c r="K9" s="4" t="str">
         <v>2021-02-18</v>
       </c>
-      <c r="L9" s="7" t="str">
+      <c r="L9" s="4" t="str">
         <v/>
       </c>
       <c r="M9" s="4" t="str">
@@ -1293,13 +1303,13 @@
       <c r="N9" s="4" t="str">
         <v>1940-01-14</v>
       </c>
-      <c r="O9" s="7">
+      <c r="O9" s="4">
         <v>78</v>
       </c>
-      <c r="P9" s="7" t="str">
-        <v/>
-      </c>
-      <c r="Q9" s="7" t="str">
+      <c r="P9" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Q9" s="4" t="str">
         <v>YEARS</v>
       </c>
       <c r="R9" s="4" t="str">
@@ -1317,10 +1327,10 @@
       <c r="V9" s="4" t="str">
         <v>Zanomaline High Dose (81 mg)</v>
       </c>
-      <c r="W9" s="7" t="str">
+      <c r="W9" s="4" t="str">
         <v>UNPLAN</v>
       </c>
-      <c r="X9" s="7" t="str">
+      <c r="X9" s="4" t="str">
         <v>Unplanned Treatment</v>
       </c>
       <c r="Y9" s="4" t="str">
@@ -1328,10 +1338,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="str">
+      <c r="A10" s="4" t="str">
         <v>ABC</v>
       </c>
-      <c r="B10" s="2" t="str">
+      <c r="B10" s="4" t="str">
         <v>DM</v>
       </c>
       <c r="C10" s="4" t="str">
@@ -1358,10 +1368,10 @@
       <c r="J10" s="4" t="str">
         <v>2018-09-04</v>
       </c>
-      <c r="K10" s="7" t="str">
+      <c r="K10" s="4" t="str">
         <v>2018-09-04</v>
       </c>
-      <c r="L10" s="7" t="str">
+      <c r="L10" s="4" t="str">
         <v>N</v>
       </c>
       <c r="M10" s="4" t="str">
@@ -1370,13 +1380,13 @@
       <c r="N10" s="4" t="str">
         <v>1947-12-23</v>
       </c>
-      <c r="O10" s="7">
+      <c r="O10" s="4">
         <v>70</v>
       </c>
-      <c r="P10" s="7" t="str">
-        <v/>
-      </c>
-      <c r="Q10" s="7" t="str">
+      <c r="P10" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Q10" s="4" t="str">
         <v>YEARS</v>
       </c>
       <c r="R10" s="4" t="str">
@@ -1405,10 +1415,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="str">
+      <c r="A11" s="4" t="str">
         <v>ABC</v>
       </c>
-      <c r="B11" s="2" t="str">
+      <c r="B11" s="4" t="str">
         <v>DM</v>
       </c>
       <c r="C11" s="4" t="str">
@@ -1435,10 +1445,10 @@
       <c r="J11" s="4" t="str">
         <v>2018-09-04</v>
       </c>
-      <c r="K11" s="7" t="str">
+      <c r="K11" s="4" t="str">
         <v>2018-09-04</v>
       </c>
-      <c r="L11" s="7" t="str">
+      <c r="L11" s="4" t="str">
         <v>N</v>
       </c>
       <c r="M11" s="4" t="str">
@@ -1447,13 +1457,13 @@
       <c r="N11" s="4" t="str">
         <v>1947-12-23</v>
       </c>
-      <c r="O11" s="7">
+      <c r="O11" s="4">
         <v>70</v>
       </c>
-      <c r="P11" s="7" t="str">
-        <v/>
-      </c>
-      <c r="Q11" s="7" t="str">
+      <c r="P11" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Q11" s="4" t="str">
         <v>YEARS</v>
       </c>
       <c r="R11" s="4" t="str">
@@ -1482,10 +1492,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="str">
+      <c r="A12" s="4" t="str">
         <v>ABC</v>
       </c>
-      <c r="B12" s="2" t="str">
+      <c r="B12" s="4" t="str">
         <v>DM</v>
       </c>
       <c r="C12" s="4" t="str">
@@ -1512,10 +1522,10 @@
       <c r="J12" s="4" t="str">
         <v>2018-09-04</v>
       </c>
-      <c r="K12" s="7" t="str">
+      <c r="K12" s="4" t="str">
         <v>2018-09-04</v>
       </c>
-      <c r="L12" s="7" t="str">
+      <c r="L12" s="4" t="str">
         <v>N</v>
       </c>
       <c r="M12" s="4" t="str">
@@ -1524,13 +1534,13 @@
       <c r="N12" s="4" t="str">
         <v>1947-12-23</v>
       </c>
-      <c r="O12" s="7">
+      <c r="O12" s="4">
         <v>70</v>
       </c>
-      <c r="P12" s="7" t="str">
-        <v/>
-      </c>
-      <c r="Q12" s="7" t="str">
+      <c r="P12" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Q12" s="4" t="str">
         <v>YEARS</v>
       </c>
       <c r="R12" s="4" t="str">
@@ -1542,10 +1552,10 @@
       <c r="T12" s="4" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="U12" s="7" t="str">
+      <c r="U12" s="4" t="str">
         <v>PLACEBO</v>
       </c>
-      <c r="V12" s="7" t="str">
+      <c r="V12" s="4" t="str">
         <v>Placebo</v>
       </c>
       <c r="W12" s="4" t="str">
@@ -1559,10 +1569,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="str">
+      <c r="A13" s="4" t="str">
         <v>ABC</v>
       </c>
-      <c r="B13" s="2" t="str">
+      <c r="B13" s="4" t="str">
         <v>DM</v>
       </c>
       <c r="C13" s="4" t="str">
@@ -1589,10 +1599,10 @@
       <c r="J13" s="4" t="str">
         <v>2018-09-04</v>
       </c>
-      <c r="K13" s="7" t="str">
+      <c r="K13" s="4" t="str">
         <v>2018-09-04</v>
       </c>
-      <c r="L13" s="7" t="str">
+      <c r="L13" s="4" t="str">
         <v>N</v>
       </c>
       <c r="M13" s="4" t="str">
@@ -1601,13 +1611,13 @@
       <c r="N13" s="4" t="str">
         <v>1947-12-23</v>
       </c>
-      <c r="O13" s="7">
+      <c r="O13" s="4">
         <v>70</v>
       </c>
-      <c r="P13" s="7" t="str">
-        <v/>
-      </c>
-      <c r="Q13" s="7" t="str">
+      <c r="P13" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Q13" s="4" t="str">
         <v>YEARS</v>
       </c>
       <c r="R13" s="4" t="str">
@@ -1636,10 +1646,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="str">
+      <c r="A14" s="4" t="str">
         <v>ABC</v>
       </c>
-      <c r="B14" s="2" t="str">
+      <c r="B14" s="4" t="str">
         <v>DM</v>
       </c>
       <c r="C14" s="4" t="str">
@@ -1666,10 +1676,10 @@
       <c r="J14" s="4" t="str">
         <v>2018-09-04</v>
       </c>
-      <c r="K14" s="7" t="str">
+      <c r="K14" s="4" t="str">
         <v>2018-09-04</v>
       </c>
-      <c r="L14" s="7" t="str">
+      <c r="L14" s="4" t="str">
         <v>N</v>
       </c>
       <c r="M14" s="4" t="str">
@@ -1678,13 +1688,13 @@
       <c r="N14" s="4" t="str">
         <v>1947-12-23</v>
       </c>
-      <c r="O14" s="7">
+      <c r="O14" s="4">
         <v>70</v>
       </c>
-      <c r="P14" s="7" t="str">
-        <v/>
-      </c>
-      <c r="Q14" s="7" t="str">
+      <c r="P14" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Q14" s="4" t="str">
         <v>YEARS</v>
       </c>
       <c r="R14" s="4" t="str">
@@ -1696,7 +1706,7 @@
       <c r="T14" s="4" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="U14" s="8" t="str">
+      <c r="U14" s="7" t="str">
         <v>ZAN_MED</v>
       </c>
       <c r="V14" s="4" t="str">
@@ -1713,10 +1723,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="str">
+      <c r="A15" s="4" t="str">
         <v>ABC</v>
       </c>
-      <c r="B15" s="2" t="str">
+      <c r="B15" s="4" t="str">
         <v>DM</v>
       </c>
       <c r="C15" s="4" t="str">
@@ -1743,10 +1753,10 @@
       <c r="J15" s="4" t="str">
         <v>2018-09-04</v>
       </c>
-      <c r="K15" s="7" t="str">
+      <c r="K15" s="4" t="str">
         <v>2018-09-04</v>
       </c>
-      <c r="L15" s="7" t="str">
+      <c r="L15" s="4" t="str">
         <v>N</v>
       </c>
       <c r="M15" s="4" t="str">
@@ -1755,13 +1765,13 @@
       <c r="N15" s="4" t="str">
         <v>1947-12-23</v>
       </c>
-      <c r="O15" s="7">
+      <c r="O15" s="4">
         <v>70</v>
       </c>
-      <c r="P15" s="7" t="str">
-        <v/>
-      </c>
-      <c r="Q15" s="7" t="str">
+      <c r="P15" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Q15" s="4" t="str">
         <v>YEARS</v>
       </c>
       <c r="R15" s="4" t="str">
@@ -1790,10 +1800,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="str">
+      <c r="A16" s="4" t="str">
         <v>ABC</v>
       </c>
-      <c r="B16" s="2" t="str">
+      <c r="B16" s="4" t="str">
         <v>DM</v>
       </c>
       <c r="C16" s="4" t="str">
@@ -1820,10 +1830,10 @@
       <c r="J16" s="4" t="str">
         <v>2018-09-04</v>
       </c>
-      <c r="K16" s="7" t="str">
+      <c r="K16" s="4" t="str">
         <v>2018-09-04</v>
       </c>
-      <c r="L16" s="7" t="str">
+      <c r="L16" s="4" t="str">
         <v>N</v>
       </c>
       <c r="M16" s="4" t="str">
@@ -1832,13 +1842,13 @@
       <c r="N16" s="4" t="str">
         <v>1947-12-23</v>
       </c>
-      <c r="O16" s="7">
+      <c r="O16" s="4">
         <v>70</v>
       </c>
-      <c r="P16" s="7" t="str">
-        <v/>
-      </c>
-      <c r="Q16" s="7" t="str">
+      <c r="P16" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Q16" s="4" t="str">
         <v>YEARS</v>
       </c>
       <c r="R16" s="4" t="str">
@@ -1850,7 +1860,7 @@
       <c r="T16" s="4" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="U16" s="4" t="str">
+      <c r="U16" s="7" t="str">
         <v/>
       </c>
       <c r="V16" s="4" t="str">
@@ -2056,31 +2066,31 @@
       <c r="A6" s="9" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B6" s="9" t="str">
+      <c r="B6" s="10" t="str">
         <v>TA</v>
       </c>
-      <c r="C6" s="9" t="str">
+      <c r="C6" s="10" t="str">
         <v>PLACEBO</v>
       </c>
-      <c r="D6" s="9" t="str">
+      <c r="D6" s="10" t="str">
         <v>Placebo</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="10">
         <v>2</v>
       </c>
-      <c r="F6" s="9" t="str">
+      <c r="F6" s="10" t="str">
         <v>PLACEBO</v>
       </c>
-      <c r="G6" s="9" t="str">
+      <c r="G6" s="10" t="str">
         <v>Placebo</v>
       </c>
-      <c r="H6" s="9" t="str">
-        <v/>
-      </c>
-      <c r="I6" s="9" t="str">
-        <v/>
-      </c>
-      <c r="J6" s="9" t="str">
+      <c r="H6" s="10" t="str">
+        <v/>
+      </c>
+      <c r="I6" s="10" t="str">
+        <v/>
+      </c>
+      <c r="J6" s="10" t="str">
         <v>TREATMENT</v>
       </c>
       <c r="K6" s="4" t="str">
@@ -2123,34 +2133,34 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="str">
+      <c r="A8" s="10" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B8" s="9" t="str">
+      <c r="B8" s="10" t="str">
         <v>TA</v>
       </c>
-      <c r="C8" s="9" t="str">
+      <c r="C8" s="10" t="str">
         <v>ZAN_LOW</v>
       </c>
-      <c r="D8" s="9" t="str">
+      <c r="D8" s="10" t="str">
         <v>Zanomaline Low Dose (54 mg)</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="10">
         <v>2</v>
       </c>
-      <c r="F8" s="9" t="str">
+      <c r="F8" s="10" t="str">
         <v>LOW</v>
       </c>
-      <c r="G8" s="9" t="str">
+      <c r="G8" s="10" t="str">
         <v>Zanomaline 54 mg</v>
       </c>
-      <c r="H8" s="9" t="str">
-        <v/>
-      </c>
-      <c r="I8" s="9" t="str">
-        <v/>
-      </c>
-      <c r="J8" s="9" t="str">
+      <c r="H8" s="10" t="str">
+        <v/>
+      </c>
+      <c r="I8" s="10" t="str">
+        <v/>
+      </c>
+      <c r="J8" s="10" t="str">
         <v>TREATMENT</v>
       </c>
       <c r="K8" s="4" t="str">
@@ -2193,34 +2203,34 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="str">
+      <c r="A10" s="10" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B10" s="9" t="str">
+      <c r="B10" s="10" t="str">
         <v>TA</v>
       </c>
-      <c r="C10" s="9" t="str">
+      <c r="C10" s="10" t="str">
         <v>ZAN_HIGH</v>
       </c>
-      <c r="D10" s="9" t="str">
+      <c r="D10" s="10" t="str">
         <v>Zanomaline High Dose (81 mg)</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="10">
         <v>2</v>
       </c>
-      <c r="F10" s="9" t="str">
+      <c r="F10" s="10" t="str">
         <v>TITRATE</v>
       </c>
-      <c r="G10" s="9" t="str">
+      <c r="G10" s="10" t="str">
         <v>Zanomaline 54 mg Titration</v>
       </c>
-      <c r="H10" s="9" t="str">
-        <v/>
-      </c>
-      <c r="I10" s="9" t="str">
-        <v/>
-      </c>
-      <c r="J10" s="9" t="str">
+      <c r="H10" s="10" t="str">
+        <v/>
+      </c>
+      <c r="I10" s="10" t="str">
+        <v/>
+      </c>
+      <c r="J10" s="10" t="str">
         <v>TREATMENT</v>
       </c>
       <c r="K10" s="4" t="str">
@@ -2263,34 +2273,34 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="str">
+      <c r="A12" s="10" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B12" s="9" t="str">
+      <c r="B12" s="10" t="str">
         <v>TA</v>
       </c>
-      <c r="C12" s="9" t="str">
+      <c r="C12" s="10" t="str">
         <v>ZAN_HIGH</v>
       </c>
-      <c r="D12" s="9" t="str">
+      <c r="D12" s="10" t="str">
         <v>Zanomaline High Dose (81 mg)</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="10">
         <v>4</v>
       </c>
-      <c r="F12" s="9" t="str">
+      <c r="F12" s="10" t="str">
         <v>TITRATE</v>
       </c>
-      <c r="G12" s="9" t="str">
+      <c r="G12" s="10" t="str">
         <v>Zanomaline 54 mg Titration</v>
       </c>
-      <c r="H12" s="9" t="str">
-        <v/>
-      </c>
-      <c r="I12" s="9" t="str">
-        <v/>
-      </c>
-      <c r="J12" s="9" t="str">
+      <c r="H12" s="10" t="str">
+        <v/>
+      </c>
+      <c r="I12" s="10" t="str">
+        <v/>
+      </c>
+      <c r="J12" s="10" t="str">
         <v>TREATMENT</v>
       </c>
       <c r="K12" s="4" t="str">
